--- a/rtss-pre1917/charts/birth-death-counts/raw-sources/Ферганская обл.xlsx
+++ b/rtss-pre1917/charts/birth-death-counts/raw-sources/Ферганская обл.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="12">
   <si>
     <t xml:space="preserve">Числа рождений и смертей для </t>
   </si>
@@ -2494,14 +2494,18 @@
         <v>1889.0</v>
       </c>
       <c r="B15" s="8" t="n">
+        <v>45339.0</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>31801.0</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8" t="n">
         <v>14229.0</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="F15" s="8" t="n">
         <v>9779.0</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
       <c r="AC15" s="3"/>
